--- a/ksoft_old/docs/records/Currency.xlsx
+++ b/ksoft_old/docs/records/Currency.xlsx
@@ -1495,13 +1495,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BB5FF70-86CB-4C57-BB7E-A4A6FE576524}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBC34C73-9103-4BDE-9783-EC2398225743}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EDD9D34-2188-4DBD-922F-066DB6E82F2F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C1FF627-2DD5-47C5-BD58-73D44338EBC3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F60332BF-1796-47EB-A871-CFBF706C35BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C413770A-F4AF-4AD3-87D5-EAD69BE5CC14}"/>
 </file>
--- a/ksoft_old/docs/records/Currency.xlsx
+++ b/ksoft_old/docs/records/Currency.xlsx
@@ -1495,13 +1495,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBC34C73-9103-4BDE-9783-EC2398225743}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02D16631-922C-49CF-A6A4-4066EDF6F215}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C1FF627-2DD5-47C5-BD58-73D44338EBC3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E018528-D26B-4B54-A011-D373BFA4BEDA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C413770A-F4AF-4AD3-87D5-EAD69BE5CC14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{776288C9-8E07-467E-BA77-444193AE1AE1}"/>
 </file>
--- a/ksoft_old/docs/records/Currency.xlsx
+++ b/ksoft_old/docs/records/Currency.xlsx
@@ -1495,13 +1495,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02D16631-922C-49CF-A6A4-4066EDF6F215}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BB5FF70-86CB-4C57-BB7E-A4A6FE576524}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E018528-D26B-4B54-A011-D373BFA4BEDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EDD9D34-2188-4DBD-922F-066DB6E82F2F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{776288C9-8E07-467E-BA77-444193AE1AE1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F60332BF-1796-47EB-A871-CFBF706C35BE}"/>
 </file>